--- a/output/pdf_financials_xlsx/MVI.H.xlsx
+++ b/output/pdf_financials_xlsx/MVI.H.xlsx
@@ -849,22 +849,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.007043</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00016</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000244</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00024</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000321</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000663</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1505,22 +1505,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-10.563541</v>
+        <v>-10.570584</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.872453</v>
+        <v>-3.872613</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.309285</v>
+        <v>2.309041</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.08315400000000001</v>
+        <v>0.082914</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.79472</v>
+        <v>1.794399</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.154125</v>
+        <v>0.153462</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.185142</v>
@@ -1585,22 +1585,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-10.563541</v>
+        <v>-10.570584</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.872453</v>
+        <v>-3.872613</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.309285</v>
+        <v>2.309041</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.08315400000000001</v>
+        <v>0.082914</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.79472</v>
+        <v>1.794399</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.154125</v>
+        <v>0.153462</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.185142</v>
@@ -1796,37 +1796,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.078413</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.180076</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.074173</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.023512</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.07394299999999999</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.029231</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.00597</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000846</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.001528</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.007032</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.013632</v>
       </c>
     </row>
     <row r="35">
@@ -1876,37 +1876,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.078413</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.180076</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.074173</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.023512</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.07394299999999999</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.029231</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.00597</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000846</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.001528</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.007032</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.013632</v>
       </c>
     </row>
     <row r="37">
@@ -2356,22 +2356,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.209872</v>
+        <v>0.131459</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.186493</v>
+        <v>0.006417</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.074173</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.023512</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.091437</v>
+        <v>0.017494</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.029231</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6740,7 +6740,11 @@
           <t>Reclamation deposit (Note 6)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -7221,7 +7225,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>0.178937</v>
       </c>
@@ -9541,7 +9549,11 @@
           <t>Decrease in reclamation deposit</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -11371,7 +11383,11 @@
           <t>(Increase) decrease in reclamation deposit</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -12519,7 +12535,11 @@
           <t>Decrease (increase) in reclamation deposit</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E96" s="5" t="n">
         <v>-0.008982</v>
       </c>
@@ -15340,7 +15360,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
@@ -16876,7 +16896,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">

--- a/output/pdf_financials_xlsx/MVI.H.xlsx
+++ b/output/pdf_financials_xlsx/MVI.H.xlsx
@@ -5113,10 +5113,10 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.174981</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.039715</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -9348,7 +9348,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -10541,7 +10545,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
